--- a/data/trans_orig/Q5415-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5415-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22638</t>
+          <t>22935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273038</t>
+          <t>272706</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>286929</t>
+          <t>286195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>307411</t>
+          <t>309734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>326713</t>
+          <t>327904</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>588515</t>
+          <t>587630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>610479</t>
+          <t>610442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>32729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30466</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54928</t>
+          <t>53259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47825</t>
+          <t>47862</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>78514</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173996</t>
+          <t>172821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191655</t>
+          <t>191374</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>256246</t>
+          <t>256698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>284440</t>
+          <t>285854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>436702</t>
+          <t>434642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>471084</t>
+          <t>470556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43824</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52381</t>
+          <t>52078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21587</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>42056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69606</t>
+          <t>71939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67379</t>
+          <t>67625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>102420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>452426</t>
+          <t>451397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>474765</t>
+          <t>473541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>573959</t>
+          <t>571277</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608800</t>
+          <t>606747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1036994</t>
+          <t>1033966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1078503</t>
+          <t>1076477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>34472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>285727</t>
+          <t>285789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300784</t>
+          <t>300978</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>315939</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>336239</t>
+          <t>336497</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>608484</t>
+          <t>607727</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>633224</t>
+          <t>633150</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>25512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45235</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75205</t>
+          <t>77340</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,47 +2837,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>74270</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>58024</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>93863</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>11,63%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>74270</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>57223</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>92858</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40819</t>
+          <t>41570</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43650</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71393</t>
+          <t>71982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69508</t>
+          <t>68708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>104715</t>
+          <t>103907</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190697</t>
+          <t>189820</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218881</t>
+          <t>218713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>253701</t>
+          <t>255823</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>290184</t>
+          <t>291561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>456727</t>
+          <t>453171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>502516</t>
+          <t>502345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54820</t>
+          <t>54005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86674</t>
+          <t>87406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73900</t>
+          <t>75643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114411</t>
+          <t>113347</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24470</t>
+          <t>24491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58899</t>
+          <t>56640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93624</t>
+          <t>90763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91036</t>
+          <t>88762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131923</t>
+          <t>128922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>483955</t>
+          <t>483579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514056</t>
+          <t>514774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>577264</t>
+          <t>578757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>620995</t>
+          <t>619559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1070977</t>
+          <t>1076362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1125797</t>
+          <t>1128499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27353</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17212</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37993</t>
+          <t>37797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310171</t>
+          <t>310411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>326152</t>
+          <t>326464</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>342109</t>
+          <t>342105</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>360914</t>
+          <t>360947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>657193</t>
+          <t>657977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>682838</t>
+          <t>683239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>22562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47799</t>
+          <t>48416</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33317</t>
+          <t>33824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61280</t>
+          <t>60408</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>28148</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54606</t>
+          <t>54481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89173</t>
+          <t>90279</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>72734</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111555</t>
+          <t>111110</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>213335</t>
+          <t>214185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>232594</t>
+          <t>233285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>275019</t>
+          <t>275448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>313841</t>
+          <t>315270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496796</t>
+          <t>496245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>542193</t>
+          <t>541176</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57206</t>
+          <t>58165</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>45126</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77370</t>
+          <t>77009</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>39016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71610</t>
+          <t>69706</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108757</t>
+          <t>107686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97923</t>
+          <t>97042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140756</t>
+          <t>138322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531396</t>
+          <t>531107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>555910</t>
+          <t>555383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>624004</t>
+          <t>626192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>670012</t>
+          <t>670607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1164210</t>
+          <t>1166110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1216266</t>
+          <t>1216752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -5522,32 +5522,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21167</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>23510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22339</t>
+          <t>26042</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37126</t>
+          <t>34570</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>42533</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>34133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52175</t>
+          <t>53037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>348537</t>
+          <t>386510</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>340388</t>
+          <t>378741</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354196</t>
+          <t>392987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>575587</t>
+          <t>401832</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>555783</t>
+          <t>391098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>594938</t>
+          <t>409412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>924124</t>
+          <t>788342</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>905744</t>
+          <t>775677</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950240</t>
+          <t>798823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>65033</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49332</t>
+          <t>54021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70180</t>
+          <t>78260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>75954</t>
+          <t>83405</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64751</t>
+          <t>71161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89977</t>
+          <t>98537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>31415</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38329</t>
+          <t>41117</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94430</t>
+          <t>102705</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82433</t>
+          <t>89955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>105509</t>
+          <t>115244</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>123982</t>
+          <t>134120</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108598</t>
+          <t>117932</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>138964</t>
+          <t>150332</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>235554</t>
+          <t>259525</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>225400</t>
+          <t>248619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>245102</t>
+          <t>269382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>271356</t>
+          <t>295809</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>257396</t>
+          <t>278751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>284527</t>
+          <t>310961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>506910</t>
+          <t>555334</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>489513</t>
+          <t>534957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>523009</t>
+          <t>573826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>424832</t>
+          <t>463547</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>424832</t>
+          <t>463547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>424832</t>
+          <t>463547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>706845</t>
+          <t>772859</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>706845</t>
+          <t>772859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706845</t>
+          <t>772859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69079</t>
+          <t>75893</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38425</t>
+          <t>63673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91914</t>
+          <t>89519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>89898</t>
+          <t>98345</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61282</t>
+          <t>84740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109599</t>
+          <t>113478</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45269</t>
+          <t>47905</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>37214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56521</t>
+          <t>59240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>116768</t>
+          <t>128747</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64041</t>
+          <t>113801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150500</t>
+          <t>146819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>162037</t>
+          <t>176652</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106753</t>
+          <t>160166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190979</t>
+          <t>197085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>584090</t>
+          <t>646034</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>570107</t>
+          <t>631946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>595297</t>
+          <t>658736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>846944</t>
+          <t>697642</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>793464</t>
+          <t>677392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>928126</t>
+          <t>716271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1431034</t>
+          <t>1343676</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1387219</t>
+          <t>1320771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1516315</t>
+          <t>1363311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1032791</t>
+          <t>902282</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1032791</t>
+          <t>902282</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1032791</t>
+          <t>902282</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1682969</t>
+          <t>1618673</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1682969</t>
+          <t>1618673</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1682969</t>
+          <t>1618673</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
